--- a/backlink-audit/disavow-review.xlsx
+++ b/backlink-audit/disavow-review.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Disavow Review'!$A$1:$L$461</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Disavow Review'!$A$1:$L$459</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3109" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3097" uniqueCount="536">
   <si>
     <t xml:space="preserve">Section</t>
   </si>
@@ -1145,436 +1145,427 @@
     <t xml:space="preserve">youtoo.in</t>
   </si>
   <si>
+    <t xml:space="preserve">SEMRUSH-ONLY - Ahrefs never crawled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100ranking.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(a)+(b)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REVIEW - single-source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semrush</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Increase Google Visibility with High Quality Backlinks ngwindows.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 dofollow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Ahrefs corroboration possible (domain not in its index). No target_url column, so evidenced by anchor text only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100ranking.link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 dofollow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1seoservices.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1seoservices.info</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7-seo.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adcreativevideo.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High Quality Dofollow Backlinks DA 50 PA 40 Premium PBN Network Service ngwindows.com Rank First</t>
+  </si>
+  <si>
+    <t xml:space="preserve">advanced-seo.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agentbetting.online</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trusted High DA Backlinks for ngwindows.com to Raise Domain Rating. Improve Google Rankings, Acr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aloysionunes.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">backlinkanalyzer.site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">backlinkcheckersite.store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">backlinkfreeseo.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">backlinkgenerator.org</t>
+  </si>
+  <si>
+    <t xml:space="preserve">backlinkmaker.info</t>
+  </si>
+  <si>
+    <t xml:space="preserve">backlinkmaker.link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">backlinkocean.info</t>
+  </si>
+  <si>
+    <t xml:space="preserve">backlinksboost.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">backlinksboost.info</t>
+  </si>
+  <si>
+    <t xml:space="preserve">backlinkscheckersite.space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">backlinksindia.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">backlinksindia.info</t>
+  </si>
+  <si>
+    <t xml:space="preserve">backlinksindia.link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">backlinkspace.info</t>
+  </si>
+  <si>
+    <t xml:space="preserve">backlinkspace.link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">backlinkspulse.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">backlinkspulse.info</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bazerdaily.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bestirishcasinoonline.online</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bestnz-poker-casinoslot.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bestonlinecasinogamescanada.online</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bestonlinecasinomexico.online</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bestseosuite.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">betwinnermirror.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bigassstadiumtourmerch.store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blog-backlinks.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blogdachecker.website</t>
+  </si>
+  <si>
+    <t xml:space="preserve">breachviews.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">burpio.shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">casinogamingsites.online</t>
+  </si>
+  <si>
+    <t xml:space="preserve">casinooftheking.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">casinoonlinecrazytime.online</t>
+  </si>
+  <si>
+    <t xml:space="preserve">casinopopular.online</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chordmp3.net</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cindylaup.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">clifflisting.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cmocheatsheets.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">competitorchecker.store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coruzants.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">daandpacheckerfree.shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dacheckeronline.shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dadpchecker.online</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dadpchecker.site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">daechul.co.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dapaseochecker.online</t>
+  </si>
+  <si>
+    <t xml:space="preserve">darankingchecker.site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">diversifiedseo.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">domainauthority.website</t>
+  </si>
+  <si>
+    <t xml:space="preserve">domainlinkprofile.site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drchecker.site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drchecker.store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drobo.shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">expresskitchendesigns.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">findbacklinks.website</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fioro.shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fittyfoody.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fletcherrld.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">freerankcheckertool.shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">geobacklinks.link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">getseotips.link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ggmap.co.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 dofollow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ggmap.us.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gladeflowers.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">go4seo.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">go4seo.info</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gofreebacklinks.info</t>
+  </si>
+  <si>
+    <t xml:space="preserve">goldbacklinks.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">goldbacklinks.info</t>
+  </si>
+  <si>
+    <t xml:space="preserve">goodbacklinkchecker.website</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gumushaneescorton.shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hotonlinegaming.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">liveserpchecker.website</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marinasone.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marketsseo.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mertio.shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">missburrg.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ninko.shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">onlineseochecker.website</t>
+  </si>
+  <si>
+    <t xml:space="preserve">onlineshoppingidea.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">perfectwebseo.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plendo.shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proseobacklinks.link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rankcheckerseo.online</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rankingschecker.site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rjcentinc.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seo-asia.link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seo-enterprise.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seo-expert-1.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seocheckerrank.site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seofastranks.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seorankingschecker.online</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seostrengthchecker.online</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seostrengthchecker.site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seotoolslike.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seowebsitechecker.site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seozens.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">serprankingchecker.site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sidarma88gacor.shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">siteseocheckerfree.store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stormbacklink.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">techbumppy.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">technicalseochecker.space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thebulkdachecker.website</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urlbacklinkchecker.store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">websiteauditchecker.space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">websitepageschecker.space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">websiterankchecker.space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">websiterankchecker.website</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disavow v2 - review summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">disavow-v2-ahrefs.txt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT FINAL - see Verdict below</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Submit as-is</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REVIEW then decide - safe to drop</t>
+  </si>
+  <si>
     <t xml:space="preserve">Auto-generated directory injection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">whosmypro.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricated geography (e.g. 'North Georgia Replacement Windows Roswell New Mexico')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">homeownerideas.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEMRUSH-ONLY - Ahrefs never crawled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100ranking.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(a)+(b)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REVIEW - single-source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Semrush</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Increase Google Visibility with High Quality Backlinks ngwindows.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 dofollow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Ahrefs corroboration possible (domain not in its index). No target_url column, so evidenced by anchor text only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100ranking.link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 dofollow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1seoservices.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1seoservices.info</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7-seo.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adcreativevideo.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High Quality Dofollow Backlinks DA 50 PA 40 Premium PBN Network Service ngwindows.com Rank First</t>
-  </si>
-  <si>
-    <t xml:space="preserve">advanced-seo.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">agentbetting.online</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trusted High DA Backlinks for ngwindows.com to Raise Domain Rating. Improve Google Rankings, Acr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aloysionunes.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">backlinkanalyzer.site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">backlinkcheckersite.store</t>
-  </si>
-  <si>
-    <t xml:space="preserve">backlinkfreeseo.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">backlinkgenerator.org</t>
-  </si>
-  <si>
-    <t xml:space="preserve">backlinkmaker.info</t>
-  </si>
-  <si>
-    <t xml:space="preserve">backlinkmaker.link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">backlinkocean.info</t>
-  </si>
-  <si>
-    <t xml:space="preserve">backlinksboost.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">backlinksboost.info</t>
-  </si>
-  <si>
-    <t xml:space="preserve">backlinkscheckersite.space</t>
-  </si>
-  <si>
-    <t xml:space="preserve">backlinksindia.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">backlinksindia.info</t>
-  </si>
-  <si>
-    <t xml:space="preserve">backlinksindia.link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">backlinkspace.info</t>
-  </si>
-  <si>
-    <t xml:space="preserve">backlinkspace.link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">backlinkspulse.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">backlinkspulse.info</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bazerdaily.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bestirishcasinoonline.online</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bestnz-poker-casinoslot.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bestonlinecasinogamescanada.online</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bestonlinecasinomexico.online</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bestseosuite.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">betwinnermirror.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bigassstadiumtourmerch.store</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blog-backlinks.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blogdachecker.website</t>
-  </si>
-  <si>
-    <t xml:space="preserve">breachviews.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">burpio.shop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">casinogamingsites.online</t>
-  </si>
-  <si>
-    <t xml:space="preserve">casinooftheking.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">casinoonlinecrazytime.online</t>
-  </si>
-  <si>
-    <t xml:space="preserve">casinopopular.online</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chordmp3.net</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cindylaup.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">clifflisting.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cmocheatsheets.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">competitorchecker.store</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coruzants.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">daandpacheckerfree.shop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dacheckeronline.shop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dadpchecker.online</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dadpchecker.site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">daechul.co.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dapaseochecker.online</t>
-  </si>
-  <si>
-    <t xml:space="preserve">darankingchecker.site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">diversifiedseo.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">domainauthority.website</t>
-  </si>
-  <si>
-    <t xml:space="preserve">domainlinkprofile.site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drchecker.site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drchecker.store</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drobo.shop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">expresskitchendesigns.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">findbacklinks.website</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fioro.shop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fittyfoody.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fletcherrld.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">freerankcheckertool.shop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">geobacklinks.link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">getseotips.link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ggmap.co.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 dofollow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ggmap.us.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gladeflowers.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">go4seo.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">go4seo.info</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gofreebacklinks.info</t>
-  </si>
-  <si>
-    <t xml:space="preserve">goldbacklinks.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">goldbacklinks.info</t>
-  </si>
-  <si>
-    <t xml:space="preserve">goodbacklinkchecker.website</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gumushaneescorton.shop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hotonlinegaming.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">liveserpchecker.website</t>
-  </si>
-  <si>
-    <t xml:space="preserve">marinasone.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">marketsseo.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mertio.shop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">missburrg.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ninko.shop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">onlineseochecker.website</t>
-  </si>
-  <si>
-    <t xml:space="preserve">onlineshoppingidea.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">perfectwebseo.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">plendo.shop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">proseobacklinks.link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rankcheckerseo.online</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rankingschecker.site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rjcentinc.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">seo-asia.link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">seo-enterprise.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">seo-expert-1.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">seocheckerrank.site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">seofastranks.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">seorankingschecker.online</t>
-  </si>
-  <si>
-    <t xml:space="preserve">seostrengthchecker.online</t>
-  </si>
-  <si>
-    <t xml:space="preserve">seostrengthchecker.site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">seotoolslike.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">seowebsitechecker.site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">seozens.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">serprankingchecker.site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sidarma88gacor.shop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">siteseocheckerfree.store</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stormbacklink.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">techbumppy.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">technicalseochecker.space</t>
-  </si>
-  <si>
-    <t xml:space="preserve">thebulkdachecker.website</t>
-  </si>
-  <si>
-    <t xml:space="preserve">urlbacklinkchecker.store</t>
-  </si>
-  <si>
-    <t xml:space="preserve">websiteauditchecker.space</t>
-  </si>
-  <si>
-    <t xml:space="preserve">websitepageschecker.space</t>
-  </si>
-  <si>
-    <t xml:space="preserve">websiterankchecker.space</t>
-  </si>
-  <si>
-    <t xml:space="preserve">websiterankchecker.website</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disavow v2 - review summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Built</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">disavow-v2-ahrefs.txt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOT FINAL - see Verdict below</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Action</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Submit as-is</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REVIEW then decide - safe to drop</t>
   </si>
   <si>
     <t xml:space="preserve">REVIEW - weakest evidence</t>
@@ -2220,7 +2211,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L461"/>
+  <dimension ref="A1:L459"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -11928,7 +11919,7 @@
     </row>
     <row r="343" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>373</v>
@@ -11937,47 +11928,55 @@
         <v>374</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="E343" s="6" t="s">
-        <v>278</v>
+        <v>375</v>
+      </c>
+      <c r="E343" s="8" t="s">
+        <v>376</v>
       </c>
       <c r="F343" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G343" s="4"/>
+        <v>377</v>
+      </c>
+      <c r="G343" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="H343" s="2"/>
-      <c r="I343" s="4"/>
+      <c r="I343" s="4" t="s">
+        <v>379</v>
+      </c>
       <c r="J343" s="4" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="K343" s="5"/>
       <c r="L343" s="4"/>
     </row>
     <row r="344" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>373</v>
       </c>
       <c r="C344" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D344" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E344" s="8" t="s">
         <v>376</v>
       </c>
-      <c r="D344" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="E344" s="6" t="s">
-        <v>278</v>
-      </c>
       <c r="F344" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G344" s="4"/>
+        <v>377</v>
+      </c>
+      <c r="G344" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="H344" s="2"/>
-      <c r="I344" s="4"/>
+      <c r="I344" s="4" t="s">
+        <v>382</v>
+      </c>
       <c r="J344" s="4" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="K344" s="5"/>
       <c r="L344" s="4"/>
@@ -11987,29 +11986,29 @@
         <v>6</v>
       </c>
       <c r="B345" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C345" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D345" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E345" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F345" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C345" s="2" t="s">
+      <c r="G345" s="4" t="s">
         <v>378</v>
-      </c>
-      <c r="D345" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E345" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F345" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="G345" s="4" t="s">
-        <v>382</v>
       </c>
       <c r="H345" s="2"/>
       <c r="I345" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J345" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K345" s="5"/>
       <c r="L345" s="4"/>
@@ -12019,29 +12018,29 @@
         <v>6</v>
       </c>
       <c r="B346" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C346" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="D346" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E346" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F346" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C346" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="D346" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E346" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F346" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G346" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H346" s="2"/>
       <c r="I346" s="4" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="J346" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K346" s="5"/>
       <c r="L346" s="4"/>
@@ -12051,29 +12050,29 @@
         <v>6</v>
       </c>
       <c r="B347" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C347" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D347" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E347" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F347" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C347" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="D347" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E347" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F347" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G347" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H347" s="2"/>
       <c r="I347" s="4" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="J347" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K347" s="5"/>
       <c r="L347" s="4"/>
@@ -12083,29 +12082,29 @@
         <v>6</v>
       </c>
       <c r="B348" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C348" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="D348" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E348" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F348" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C348" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="D348" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E348" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F348" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G348" s="4" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="H348" s="2"/>
       <c r="I348" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J348" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K348" s="5"/>
       <c r="L348" s="4"/>
@@ -12115,29 +12114,29 @@
         <v>6</v>
       </c>
       <c r="B349" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C349" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="D349" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E349" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F349" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C349" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="D349" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E349" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F349" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G349" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H349" s="2"/>
       <c r="I349" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J349" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K349" s="5"/>
       <c r="L349" s="4"/>
@@ -12147,29 +12146,29 @@
         <v>6</v>
       </c>
       <c r="B350" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C350" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="D350" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E350" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F350" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C350" s="2" t="s">
+      <c r="G350" s="4" t="s">
         <v>390</v>
-      </c>
-      <c r="D350" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E350" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F350" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="G350" s="4" t="s">
-        <v>391</v>
       </c>
       <c r="H350" s="2"/>
       <c r="I350" s="4" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="J350" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K350" s="5"/>
       <c r="L350" s="4"/>
@@ -12179,29 +12178,29 @@
         <v>6</v>
       </c>
       <c r="B351" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C351" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="D351" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E351" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F351" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C351" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="D351" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E351" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F351" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G351" s="4" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="H351" s="2"/>
       <c r="I351" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J351" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K351" s="5"/>
       <c r="L351" s="4"/>
@@ -12211,29 +12210,29 @@
         <v>6</v>
       </c>
       <c r="B352" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C352" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="D352" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E352" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F352" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C352" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="D352" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E352" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F352" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G352" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="H352" s="2"/>
       <c r="I352" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J352" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K352" s="5"/>
       <c r="L352" s="4"/>
@@ -12243,29 +12242,29 @@
         <v>6</v>
       </c>
       <c r="B353" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C353" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="D353" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E353" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F353" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C353" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="D353" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E353" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F353" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G353" s="4" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="H353" s="2"/>
       <c r="I353" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J353" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K353" s="5"/>
       <c r="L353" s="4"/>
@@ -12275,29 +12274,29 @@
         <v>6</v>
       </c>
       <c r="B354" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C354" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="D354" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E354" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F354" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C354" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="D354" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E354" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F354" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G354" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H354" s="2"/>
       <c r="I354" s="4" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="J354" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K354" s="5"/>
       <c r="L354" s="4"/>
@@ -12307,29 +12306,29 @@
         <v>6</v>
       </c>
       <c r="B355" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C355" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="D355" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E355" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F355" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C355" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="D355" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E355" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F355" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G355" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H355" s="2"/>
       <c r="I355" s="4" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="J355" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K355" s="5"/>
       <c r="L355" s="4"/>
@@ -12339,29 +12338,29 @@
         <v>6</v>
       </c>
       <c r="B356" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C356" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D356" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E356" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F356" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C356" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="D356" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E356" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F356" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G356" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H356" s="2"/>
       <c r="I356" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J356" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K356" s="5"/>
       <c r="L356" s="4"/>
@@ -12371,29 +12370,29 @@
         <v>6</v>
       </c>
       <c r="B357" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C357" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D357" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E357" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F357" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C357" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="D357" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E357" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F357" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G357" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H357" s="2"/>
       <c r="I357" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J357" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K357" s="5"/>
       <c r="L357" s="4"/>
@@ -12403,29 +12402,29 @@
         <v>6</v>
       </c>
       <c r="B358" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C358" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D358" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E358" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F358" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C358" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="D358" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E358" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F358" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G358" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H358" s="2"/>
       <c r="I358" s="4" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="J358" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K358" s="5"/>
       <c r="L358" s="4"/>
@@ -12435,29 +12434,29 @@
         <v>6</v>
       </c>
       <c r="B359" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C359" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="D359" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E359" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F359" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C359" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="D359" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E359" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F359" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G359" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H359" s="2"/>
       <c r="I359" s="4" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="J359" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K359" s="5"/>
       <c r="L359" s="4"/>
@@ -12467,29 +12466,29 @@
         <v>6</v>
       </c>
       <c r="B360" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C360" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="D360" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E360" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F360" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C360" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="D360" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E360" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F360" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G360" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H360" s="2"/>
       <c r="I360" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J360" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K360" s="5"/>
       <c r="L360" s="4"/>
@@ -12499,29 +12498,29 @@
         <v>6</v>
       </c>
       <c r="B361" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C361" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="D361" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E361" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F361" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C361" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="D361" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E361" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F361" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G361" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H361" s="2"/>
       <c r="I361" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J361" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K361" s="5"/>
       <c r="L361" s="4"/>
@@ -12531,29 +12530,29 @@
         <v>6</v>
       </c>
       <c r="B362" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C362" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="D362" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E362" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F362" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C362" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="D362" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E362" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F362" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G362" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H362" s="2"/>
       <c r="I362" s="4" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="J362" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K362" s="5"/>
       <c r="L362" s="4"/>
@@ -12563,29 +12562,29 @@
         <v>6</v>
       </c>
       <c r="B363" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C363" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="D363" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E363" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F363" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C363" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="D363" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E363" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F363" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G363" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H363" s="2"/>
       <c r="I363" s="4" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="J363" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K363" s="5"/>
       <c r="L363" s="4"/>
@@ -12595,29 +12594,29 @@
         <v>6</v>
       </c>
       <c r="B364" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C364" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="D364" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E364" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F364" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C364" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="D364" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E364" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F364" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G364" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H364" s="2"/>
       <c r="I364" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J364" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K364" s="5"/>
       <c r="L364" s="4"/>
@@ -12627,29 +12626,29 @@
         <v>6</v>
       </c>
       <c r="B365" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C365" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="D365" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E365" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F365" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C365" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="D365" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E365" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F365" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G365" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H365" s="2"/>
       <c r="I365" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J365" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K365" s="5"/>
       <c r="L365" s="4"/>
@@ -12659,29 +12658,29 @@
         <v>6</v>
       </c>
       <c r="B366" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C366" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="D366" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E366" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F366" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C366" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="D366" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E366" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F366" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G366" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H366" s="2"/>
       <c r="I366" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J366" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K366" s="5"/>
       <c r="L366" s="4"/>
@@ -12691,29 +12690,29 @@
         <v>6</v>
       </c>
       <c r="B367" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C367" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D367" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E367" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F367" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C367" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="D367" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E367" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F367" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G367" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H367" s="2"/>
       <c r="I367" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J367" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K367" s="5"/>
       <c r="L367" s="4"/>
@@ -12723,29 +12722,29 @@
         <v>6</v>
       </c>
       <c r="B368" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C368" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D368" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E368" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F368" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C368" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="D368" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E368" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F368" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G368" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H368" s="2"/>
       <c r="I368" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J368" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K368" s="5"/>
       <c r="L368" s="4"/>
@@ -12755,29 +12754,29 @@
         <v>6</v>
       </c>
       <c r="B369" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C369" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="D369" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E369" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F369" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C369" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="D369" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E369" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F369" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G369" s="4" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="H369" s="2"/>
       <c r="I369" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J369" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K369" s="5"/>
       <c r="L369" s="4"/>
@@ -12787,29 +12786,29 @@
         <v>6</v>
       </c>
       <c r="B370" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C370" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="D370" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E370" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F370" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C370" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="D370" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E370" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F370" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G370" s="4" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="H370" s="2"/>
       <c r="I370" s="4" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="J370" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K370" s="5"/>
       <c r="L370" s="4"/>
@@ -12819,29 +12818,29 @@
         <v>6</v>
       </c>
       <c r="B371" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C371" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="D371" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E371" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F371" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C371" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="D371" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E371" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F371" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G371" s="4" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="H371" s="2"/>
       <c r="I371" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J371" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K371" s="5"/>
       <c r="L371" s="4"/>
@@ -12851,29 +12850,29 @@
         <v>6</v>
       </c>
       <c r="B372" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C372" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="D372" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E372" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F372" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C372" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="D372" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E372" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F372" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G372" s="4" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="H372" s="2"/>
       <c r="I372" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J372" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K372" s="5"/>
       <c r="L372" s="4"/>
@@ -12883,29 +12882,29 @@
         <v>6</v>
       </c>
       <c r="B373" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C373" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="D373" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E373" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F373" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C373" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="D373" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E373" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F373" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G373" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H373" s="2"/>
       <c r="I373" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J373" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K373" s="5"/>
       <c r="L373" s="4"/>
@@ -12915,29 +12914,29 @@
         <v>6</v>
       </c>
       <c r="B374" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C374" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="D374" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E374" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F374" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C374" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="D374" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E374" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F374" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G374" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="H374" s="2"/>
       <c r="I374" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J374" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K374" s="5"/>
       <c r="L374" s="4"/>
@@ -12947,29 +12946,29 @@
         <v>6</v>
       </c>
       <c r="B375" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C375" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="D375" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E375" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F375" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C375" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="D375" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E375" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F375" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G375" s="4" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="H375" s="2"/>
       <c r="I375" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J375" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K375" s="5"/>
       <c r="L375" s="4"/>
@@ -12979,29 +12978,29 @@
         <v>6</v>
       </c>
       <c r="B376" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C376" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="D376" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E376" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F376" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C376" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="D376" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E376" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F376" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G376" s="4" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="H376" s="2"/>
       <c r="I376" s="4" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="J376" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K376" s="5"/>
       <c r="L376" s="4"/>
@@ -13011,29 +13010,29 @@
         <v>6</v>
       </c>
       <c r="B377" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C377" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D377" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E377" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F377" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C377" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="D377" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E377" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F377" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G377" s="4" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="H377" s="2"/>
       <c r="I377" s="4" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="J377" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K377" s="5"/>
       <c r="L377" s="4"/>
@@ -13043,29 +13042,29 @@
         <v>6</v>
       </c>
       <c r="B378" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C378" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="D378" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E378" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F378" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C378" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="D378" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E378" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F378" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G378" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="H378" s="2"/>
       <c r="I378" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J378" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K378" s="5"/>
       <c r="L378" s="4"/>
@@ -13075,29 +13074,29 @@
         <v>6</v>
       </c>
       <c r="B379" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C379" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="D379" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E379" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F379" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C379" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="D379" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E379" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F379" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G379" s="4" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="H379" s="2"/>
       <c r="I379" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J379" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K379" s="5"/>
       <c r="L379" s="4"/>
@@ -13107,29 +13106,29 @@
         <v>6</v>
       </c>
       <c r="B380" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C380" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="D380" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E380" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F380" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C380" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="D380" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E380" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F380" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G380" s="4" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="H380" s="2"/>
       <c r="I380" s="4" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="J380" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K380" s="5"/>
       <c r="L380" s="4"/>
@@ -13139,29 +13138,29 @@
         <v>6</v>
       </c>
       <c r="B381" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C381" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="D381" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E381" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F381" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C381" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="D381" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E381" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F381" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G381" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H381" s="2"/>
       <c r="I381" s="4" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="J381" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K381" s="5"/>
       <c r="L381" s="4"/>
@@ -13171,29 +13170,29 @@
         <v>6</v>
       </c>
       <c r="B382" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C382" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="D382" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E382" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F382" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C382" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="D382" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E382" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F382" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G382" s="4" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="H382" s="2"/>
       <c r="I382" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J382" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K382" s="5"/>
       <c r="L382" s="4"/>
@@ -13203,29 +13202,29 @@
         <v>6</v>
       </c>
       <c r="B383" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C383" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="D383" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E383" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F383" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C383" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="D383" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E383" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F383" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G383" s="4" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="H383" s="2"/>
       <c r="I383" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J383" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K383" s="5"/>
       <c r="L383" s="4"/>
@@ -13235,29 +13234,29 @@
         <v>6</v>
       </c>
       <c r="B384" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C384" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="D384" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E384" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F384" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C384" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="D384" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E384" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F384" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G384" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H384" s="2"/>
       <c r="I384" s="4" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="J384" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K384" s="5"/>
       <c r="L384" s="4"/>
@@ -13267,29 +13266,29 @@
         <v>6</v>
       </c>
       <c r="B385" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C385" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="D385" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E385" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F385" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C385" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="D385" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E385" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F385" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G385" s="4" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="H385" s="2"/>
       <c r="I385" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J385" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K385" s="5"/>
       <c r="L385" s="4"/>
@@ -13299,29 +13298,29 @@
         <v>6</v>
       </c>
       <c r="B386" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C386" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D386" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E386" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F386" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C386" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="D386" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E386" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F386" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G386" s="4" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="H386" s="2"/>
       <c r="I386" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J386" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K386" s="5"/>
       <c r="L386" s="4"/>
@@ -13331,29 +13330,29 @@
         <v>6</v>
       </c>
       <c r="B387" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C387" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="D387" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E387" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F387" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C387" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="D387" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E387" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F387" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G387" s="4" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="H387" s="2"/>
       <c r="I387" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J387" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K387" s="5"/>
       <c r="L387" s="4"/>
@@ -13363,29 +13362,29 @@
         <v>6</v>
       </c>
       <c r="B388" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C388" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D388" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E388" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F388" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C388" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="D388" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E388" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F388" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G388" s="4" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="H388" s="2"/>
       <c r="I388" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J388" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K388" s="5"/>
       <c r="L388" s="4"/>
@@ -13395,29 +13394,29 @@
         <v>6</v>
       </c>
       <c r="B389" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C389" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="D389" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E389" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F389" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C389" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="D389" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E389" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F389" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G389" s="4" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="H389" s="2"/>
       <c r="I389" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J389" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K389" s="5"/>
       <c r="L389" s="4"/>
@@ -13427,29 +13426,29 @@
         <v>6</v>
       </c>
       <c r="B390" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C390" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="D390" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E390" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F390" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C390" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="D390" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E390" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F390" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G390" s="4" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="H390" s="2"/>
       <c r="I390" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J390" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K390" s="5"/>
       <c r="L390" s="4"/>
@@ -13459,29 +13458,29 @@
         <v>6</v>
       </c>
       <c r="B391" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C391" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="D391" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E391" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F391" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C391" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="D391" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E391" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F391" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G391" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H391" s="2"/>
       <c r="I391" s="4" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="J391" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K391" s="5"/>
       <c r="L391" s="4"/>
@@ -13491,29 +13490,29 @@
         <v>6</v>
       </c>
       <c r="B392" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C392" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="D392" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E392" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F392" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C392" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="D392" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E392" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F392" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G392" s="4" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="H392" s="2"/>
       <c r="I392" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J392" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K392" s="5"/>
       <c r="L392" s="4"/>
@@ -13523,29 +13522,29 @@
         <v>6</v>
       </c>
       <c r="B393" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C393" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="D393" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E393" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F393" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C393" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="D393" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E393" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F393" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G393" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H393" s="2"/>
       <c r="I393" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J393" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K393" s="5"/>
       <c r="L393" s="4"/>
@@ -13555,29 +13554,29 @@
         <v>6</v>
       </c>
       <c r="B394" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C394" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="D394" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E394" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F394" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C394" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="D394" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E394" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F394" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G394" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H394" s="2"/>
       <c r="I394" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J394" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K394" s="5"/>
       <c r="L394" s="4"/>
@@ -13587,29 +13586,29 @@
         <v>6</v>
       </c>
       <c r="B395" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C395" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="D395" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E395" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F395" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C395" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="D395" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E395" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F395" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G395" s="4" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="H395" s="2"/>
       <c r="I395" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J395" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K395" s="5"/>
       <c r="L395" s="4"/>
@@ -13619,29 +13618,29 @@
         <v>6</v>
       </c>
       <c r="B396" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C396" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D396" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E396" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F396" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C396" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="D396" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E396" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F396" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G396" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H396" s="2"/>
       <c r="I396" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J396" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K396" s="5"/>
       <c r="L396" s="4"/>
@@ -13651,29 +13650,29 @@
         <v>6</v>
       </c>
       <c r="B397" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C397" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D397" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E397" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F397" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C397" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="D397" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E397" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F397" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G397" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="H397" s="2"/>
       <c r="I397" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J397" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K397" s="5"/>
       <c r="L397" s="4"/>
@@ -13683,29 +13682,29 @@
         <v>6</v>
       </c>
       <c r="B398" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C398" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="D398" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E398" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F398" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C398" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="D398" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E398" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F398" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G398" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H398" s="2"/>
       <c r="I398" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J398" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K398" s="5"/>
       <c r="L398" s="4"/>
@@ -13715,29 +13714,29 @@
         <v>6</v>
       </c>
       <c r="B399" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C399" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="D399" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E399" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F399" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C399" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="D399" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E399" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F399" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G399" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H399" s="2"/>
       <c r="I399" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J399" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K399" s="5"/>
       <c r="L399" s="4"/>
@@ -13747,29 +13746,29 @@
         <v>6</v>
       </c>
       <c r="B400" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C400" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D400" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E400" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F400" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C400" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="D400" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E400" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F400" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G400" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H400" s="2"/>
       <c r="I400" s="4" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="J400" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K400" s="5"/>
       <c r="L400" s="4"/>
@@ -13779,29 +13778,29 @@
         <v>6</v>
       </c>
       <c r="B401" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C401" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="D401" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E401" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F401" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C401" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="D401" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E401" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F401" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G401" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H401" s="2"/>
       <c r="I401" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J401" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K401" s="5"/>
       <c r="L401" s="4"/>
@@ -13811,29 +13810,29 @@
         <v>6</v>
       </c>
       <c r="B402" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C402" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="D402" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E402" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F402" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C402" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="D402" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E402" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F402" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G402" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H402" s="2"/>
       <c r="I402" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J402" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K402" s="5"/>
       <c r="L402" s="4"/>
@@ -13843,29 +13842,29 @@
         <v>6</v>
       </c>
       <c r="B403" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C403" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="D403" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E403" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F403" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C403" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="D403" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E403" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F403" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G403" s="4" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="H403" s="2"/>
       <c r="I403" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J403" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K403" s="5"/>
       <c r="L403" s="4"/>
@@ -13875,29 +13874,29 @@
         <v>6</v>
       </c>
       <c r="B404" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C404" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="D404" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E404" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F404" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C404" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="D404" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E404" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F404" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G404" s="4" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="H404" s="2"/>
       <c r="I404" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J404" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K404" s="5"/>
       <c r="L404" s="4"/>
@@ -13907,29 +13906,29 @@
         <v>6</v>
       </c>
       <c r="B405" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C405" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="D405" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E405" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F405" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C405" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="D405" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E405" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F405" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G405" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="H405" s="2"/>
       <c r="I405" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J405" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K405" s="5"/>
       <c r="L405" s="4"/>
@@ -13939,29 +13938,29 @@
         <v>6</v>
       </c>
       <c r="B406" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C406" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="D406" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E406" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F406" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C406" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="D406" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E406" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F406" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G406" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H406" s="2"/>
       <c r="I406" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J406" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K406" s="5"/>
       <c r="L406" s="4"/>
@@ -13971,29 +13970,29 @@
         <v>6</v>
       </c>
       <c r="B407" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C407" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D407" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E407" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F407" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C407" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="D407" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E407" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F407" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G407" s="4" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="H407" s="2"/>
       <c r="I407" s="4" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="J407" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K407" s="5"/>
       <c r="L407" s="4"/>
@@ -14003,29 +14002,29 @@
         <v>6</v>
       </c>
       <c r="B408" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C408" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="D408" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E408" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F408" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C408" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="D408" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E408" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F408" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G408" s="4" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="H408" s="2"/>
       <c r="I408" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J408" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K408" s="5"/>
       <c r="L408" s="4"/>
@@ -14035,29 +14034,29 @@
         <v>6</v>
       </c>
       <c r="B409" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C409" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="D409" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E409" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F409" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C409" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="D409" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E409" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F409" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G409" s="4" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="H409" s="2"/>
       <c r="I409" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J409" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K409" s="5"/>
       <c r="L409" s="4"/>
@@ -14067,29 +14066,29 @@
         <v>6</v>
       </c>
       <c r="B410" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C410" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D410" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E410" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F410" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C410" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="D410" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E410" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F410" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G410" s="4" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="H410" s="2"/>
       <c r="I410" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J410" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K410" s="5"/>
       <c r="L410" s="4"/>
@@ -14099,29 +14098,29 @@
         <v>6</v>
       </c>
       <c r="B411" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C411" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="D411" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E411" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F411" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C411" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="D411" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E411" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F411" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G411" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H411" s="2"/>
       <c r="I411" s="4" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="J411" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K411" s="5"/>
       <c r="L411" s="4"/>
@@ -14131,29 +14130,29 @@
         <v>6</v>
       </c>
       <c r="B412" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C412" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D412" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E412" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F412" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C412" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="D412" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E412" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F412" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G412" s="4" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="H412" s="2"/>
       <c r="I412" s="4" t="s">
-        <v>383</v>
+        <v>453</v>
       </c>
       <c r="J412" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K412" s="5"/>
       <c r="L412" s="4"/>
@@ -14163,29 +14162,29 @@
         <v>6</v>
       </c>
       <c r="B413" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C413" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="D413" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E413" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F413" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C413" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="D413" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E413" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F413" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G413" s="4" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="H413" s="2"/>
       <c r="I413" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J413" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K413" s="5"/>
       <c r="L413" s="4"/>
@@ -14195,29 +14194,29 @@
         <v>6</v>
       </c>
       <c r="B414" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C414" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D414" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E414" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F414" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C414" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="D414" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E414" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F414" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G414" s="4" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="H414" s="2"/>
       <c r="I414" s="4" t="s">
-        <v>457</v>
+        <v>382</v>
       </c>
       <c r="J414" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K414" s="5"/>
       <c r="L414" s="4"/>
@@ -14227,29 +14226,29 @@
         <v>6</v>
       </c>
       <c r="B415" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C415" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D415" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E415" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F415" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C415" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="D415" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E415" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F415" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G415" s="4" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="H415" s="2"/>
       <c r="I415" s="4" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="J415" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K415" s="5"/>
       <c r="L415" s="4"/>
@@ -14259,29 +14258,29 @@
         <v>6</v>
       </c>
       <c r="B416" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C416" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="D416" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E416" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F416" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C416" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="D416" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E416" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F416" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G416" s="4" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="H416" s="2"/>
       <c r="I416" s="4" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="J416" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K416" s="5"/>
       <c r="L416" s="4"/>
@@ -14291,29 +14290,29 @@
         <v>6</v>
       </c>
       <c r="B417" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C417" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D417" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E417" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F417" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C417" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="D417" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E417" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F417" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G417" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H417" s="2"/>
       <c r="I417" s="4" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="J417" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K417" s="5"/>
       <c r="L417" s="4"/>
@@ -14323,29 +14322,29 @@
         <v>6</v>
       </c>
       <c r="B418" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C418" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D418" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E418" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F418" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C418" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="D418" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E418" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F418" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G418" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H418" s="2"/>
       <c r="I418" s="4" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="J418" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K418" s="5"/>
       <c r="L418" s="4"/>
@@ -14355,29 +14354,29 @@
         <v>6</v>
       </c>
       <c r="B419" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C419" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D419" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E419" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F419" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C419" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="D419" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E419" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F419" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G419" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H419" s="2"/>
       <c r="I419" s="4" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="J419" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K419" s="5"/>
       <c r="L419" s="4"/>
@@ -14387,29 +14386,29 @@
         <v>6</v>
       </c>
       <c r="B420" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C420" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D420" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E420" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F420" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C420" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="D420" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E420" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F420" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G420" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H420" s="2"/>
       <c r="I420" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J420" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K420" s="5"/>
       <c r="L420" s="4"/>
@@ -14419,29 +14418,29 @@
         <v>6</v>
       </c>
       <c r="B421" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C421" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D421" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E421" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F421" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C421" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="D421" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E421" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F421" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G421" s="4" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="H421" s="2"/>
       <c r="I421" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J421" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K421" s="5"/>
       <c r="L421" s="4"/>
@@ -14451,29 +14450,29 @@
         <v>6</v>
       </c>
       <c r="B422" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C422" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D422" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E422" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F422" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C422" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="D422" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E422" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F422" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G422" s="4" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="H422" s="2"/>
       <c r="I422" s="4" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="J422" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K422" s="5"/>
       <c r="L422" s="4"/>
@@ -14483,29 +14482,29 @@
         <v>6</v>
       </c>
       <c r="B423" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C423" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D423" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E423" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F423" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C423" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="D423" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E423" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F423" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G423" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="H423" s="2"/>
       <c r="I423" s="4" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="J423" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K423" s="5"/>
       <c r="L423" s="4"/>
@@ -14515,29 +14514,29 @@
         <v>6</v>
       </c>
       <c r="B424" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C424" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="D424" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E424" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F424" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C424" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="D424" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E424" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F424" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G424" s="4" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="H424" s="2"/>
       <c r="I424" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J424" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K424" s="5"/>
       <c r="L424" s="4"/>
@@ -14547,29 +14546,29 @@
         <v>6</v>
       </c>
       <c r="B425" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C425" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="D425" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E425" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F425" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C425" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="D425" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E425" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F425" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G425" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H425" s="2"/>
       <c r="I425" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J425" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K425" s="5"/>
       <c r="L425" s="4"/>
@@ -14579,29 +14578,29 @@
         <v>6</v>
       </c>
       <c r="B426" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C426" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D426" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E426" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F426" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C426" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="D426" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E426" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F426" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G426" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H426" s="2"/>
       <c r="I426" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J426" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K426" s="5"/>
       <c r="L426" s="4"/>
@@ -14611,29 +14610,29 @@
         <v>6</v>
       </c>
       <c r="B427" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C427" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="D427" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E427" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F427" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C427" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="D427" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E427" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F427" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G427" s="4" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="H427" s="2"/>
       <c r="I427" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J427" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K427" s="5"/>
       <c r="L427" s="4"/>
@@ -14643,29 +14642,29 @@
         <v>6</v>
       </c>
       <c r="B428" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C428" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D428" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E428" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F428" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C428" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="D428" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E428" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F428" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G428" s="4" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="H428" s="2"/>
       <c r="I428" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J428" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K428" s="5"/>
       <c r="L428" s="4"/>
@@ -14675,29 +14674,29 @@
         <v>6</v>
       </c>
       <c r="B429" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C429" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="D429" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E429" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F429" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C429" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="D429" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E429" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F429" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G429" s="4" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="H429" s="2"/>
       <c r="I429" s="4" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="J429" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K429" s="5"/>
       <c r="L429" s="4"/>
@@ -14707,29 +14706,29 @@
         <v>6</v>
       </c>
       <c r="B430" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C430" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D430" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E430" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F430" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C430" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="D430" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E430" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F430" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G430" s="4" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="H430" s="2"/>
       <c r="I430" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J430" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K430" s="5"/>
       <c r="L430" s="4"/>
@@ -14739,29 +14738,29 @@
         <v>6</v>
       </c>
       <c r="B431" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C431" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="D431" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E431" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F431" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C431" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="D431" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E431" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F431" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G431" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H431" s="2"/>
       <c r="I431" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J431" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K431" s="5"/>
       <c r="L431" s="4"/>
@@ -14771,29 +14770,29 @@
         <v>6</v>
       </c>
       <c r="B432" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C432" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D432" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E432" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F432" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C432" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="D432" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E432" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F432" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G432" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H432" s="2"/>
       <c r="I432" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J432" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K432" s="5"/>
       <c r="L432" s="4"/>
@@ -14803,29 +14802,29 @@
         <v>6</v>
       </c>
       <c r="B433" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C433" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D433" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E433" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F433" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C433" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="D433" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E433" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F433" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G433" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H433" s="2"/>
       <c r="I433" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J433" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K433" s="5"/>
       <c r="L433" s="4"/>
@@ -14835,29 +14834,29 @@
         <v>6</v>
       </c>
       <c r="B434" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C434" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="D434" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E434" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F434" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C434" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="D434" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E434" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F434" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G434" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="H434" s="2"/>
       <c r="I434" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J434" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K434" s="5"/>
       <c r="L434" s="4"/>
@@ -14867,29 +14866,29 @@
         <v>6</v>
       </c>
       <c r="B435" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C435" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D435" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E435" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F435" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C435" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="D435" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E435" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F435" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G435" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H435" s="2"/>
       <c r="I435" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J435" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K435" s="5"/>
       <c r="L435" s="4"/>
@@ -14899,29 +14898,29 @@
         <v>6</v>
       </c>
       <c r="B436" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C436" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D436" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E436" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F436" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C436" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="D436" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E436" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F436" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G436" s="4" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="H436" s="2"/>
       <c r="I436" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J436" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K436" s="5"/>
       <c r="L436" s="4"/>
@@ -14931,29 +14930,29 @@
         <v>6</v>
       </c>
       <c r="B437" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C437" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="D437" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E437" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F437" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C437" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="D437" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E437" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F437" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G437" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H437" s="2"/>
       <c r="I437" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J437" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K437" s="5"/>
       <c r="L437" s="4"/>
@@ -14963,29 +14962,29 @@
         <v>6</v>
       </c>
       <c r="B438" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C438" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="D438" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E438" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F438" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C438" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="D438" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E438" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F438" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G438" s="4" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="H438" s="2"/>
       <c r="I438" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J438" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K438" s="5"/>
       <c r="L438" s="4"/>
@@ -14995,29 +14994,29 @@
         <v>6</v>
       </c>
       <c r="B439" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C439" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="D439" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E439" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F439" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C439" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="D439" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E439" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F439" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G439" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H439" s="2"/>
       <c r="I439" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J439" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K439" s="5"/>
       <c r="L439" s="4"/>
@@ -15027,29 +15026,29 @@
         <v>6</v>
       </c>
       <c r="B440" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C440" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="D440" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E440" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F440" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C440" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="D440" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E440" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F440" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G440" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H440" s="2"/>
       <c r="I440" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J440" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K440" s="5"/>
       <c r="L440" s="4"/>
@@ -15059,29 +15058,29 @@
         <v>6</v>
       </c>
       <c r="B441" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C441" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D441" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E441" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F441" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C441" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="D441" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E441" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F441" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G441" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H441" s="2"/>
       <c r="I441" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J441" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K441" s="5"/>
       <c r="L441" s="4"/>
@@ -15091,29 +15090,29 @@
         <v>6</v>
       </c>
       <c r="B442" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C442" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="D442" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E442" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F442" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C442" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="D442" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E442" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F442" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G442" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H442" s="2"/>
       <c r="I442" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J442" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K442" s="5"/>
       <c r="L442" s="4"/>
@@ -15123,29 +15122,29 @@
         <v>6</v>
       </c>
       <c r="B443" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C443" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="D443" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E443" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F443" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C443" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="D443" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E443" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F443" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G443" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H443" s="2"/>
       <c r="I443" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J443" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K443" s="5"/>
       <c r="L443" s="4"/>
@@ -15155,29 +15154,29 @@
         <v>6</v>
       </c>
       <c r="B444" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C444" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="D444" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E444" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F444" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C444" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D444" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E444" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F444" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G444" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H444" s="2"/>
       <c r="I444" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J444" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K444" s="5"/>
       <c r="L444" s="4"/>
@@ -15187,29 +15186,29 @@
         <v>6</v>
       </c>
       <c r="B445" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C445" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="D445" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E445" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F445" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C445" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="D445" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E445" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F445" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G445" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H445" s="2"/>
       <c r="I445" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J445" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K445" s="5"/>
       <c r="L445" s="4"/>
@@ -15219,29 +15218,29 @@
         <v>6</v>
       </c>
       <c r="B446" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C446" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D446" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E446" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F446" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C446" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="D446" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E446" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F446" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G446" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H446" s="2"/>
       <c r="I446" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J446" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K446" s="5"/>
       <c r="L446" s="4"/>
@@ -15251,29 +15250,29 @@
         <v>6</v>
       </c>
       <c r="B447" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C447" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="D447" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E447" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F447" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C447" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="D447" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E447" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F447" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G447" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H447" s="2"/>
       <c r="I447" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J447" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K447" s="5"/>
       <c r="L447" s="4"/>
@@ -15283,29 +15282,29 @@
         <v>6</v>
       </c>
       <c r="B448" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C448" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="D448" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E448" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F448" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C448" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="D448" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E448" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F448" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G448" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H448" s="2"/>
       <c r="I448" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J448" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K448" s="5"/>
       <c r="L448" s="4"/>
@@ -15315,29 +15314,29 @@
         <v>6</v>
       </c>
       <c r="B449" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C449" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D449" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E449" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F449" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C449" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="D449" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E449" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F449" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G449" s="4" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="H449" s="2"/>
       <c r="I449" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J449" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K449" s="5"/>
       <c r="L449" s="4"/>
@@ -15347,29 +15346,29 @@
         <v>6</v>
       </c>
       <c r="B450" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C450" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="D450" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E450" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F450" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C450" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="D450" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E450" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F450" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G450" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H450" s="2"/>
       <c r="I450" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J450" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K450" s="5"/>
       <c r="L450" s="4"/>
@@ -15379,29 +15378,29 @@
         <v>6</v>
       </c>
       <c r="B451" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C451" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="D451" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E451" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F451" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C451" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="D451" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E451" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F451" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G451" s="4" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="H451" s="2"/>
       <c r="I451" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J451" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K451" s="5"/>
       <c r="L451" s="4"/>
@@ -15411,29 +15410,29 @@
         <v>6</v>
       </c>
       <c r="B452" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C452" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D452" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E452" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F452" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C452" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="D452" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E452" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F452" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G452" s="4" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="H452" s="2"/>
       <c r="I452" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J452" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K452" s="5"/>
       <c r="L452" s="4"/>
@@ -15443,29 +15442,29 @@
         <v>6</v>
       </c>
       <c r="B453" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C453" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="D453" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E453" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F453" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C453" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="D453" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E453" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F453" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G453" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H453" s="2"/>
       <c r="I453" s="4" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="J453" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K453" s="5"/>
       <c r="L453" s="4"/>
@@ -15475,29 +15474,29 @@
         <v>6</v>
       </c>
       <c r="B454" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C454" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D454" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E454" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F454" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C454" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="D454" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E454" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F454" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G454" s="4" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="H454" s="2"/>
       <c r="I454" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J454" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K454" s="5"/>
       <c r="L454" s="4"/>
@@ -15507,29 +15506,29 @@
         <v>6</v>
       </c>
       <c r="B455" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C455" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="D455" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E455" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F455" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C455" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="D455" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E455" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F455" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G455" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H455" s="2"/>
       <c r="I455" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J455" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K455" s="5"/>
       <c r="L455" s="4"/>
@@ -15539,29 +15538,29 @@
         <v>6</v>
       </c>
       <c r="B456" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C456" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="D456" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E456" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F456" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C456" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="D456" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E456" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F456" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G456" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H456" s="2"/>
       <c r="I456" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J456" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K456" s="5"/>
       <c r="L456" s="4"/>
@@ -15571,29 +15570,29 @@
         <v>6</v>
       </c>
       <c r="B457" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C457" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="D457" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E457" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F457" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C457" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="D457" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E457" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F457" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G457" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H457" s="2"/>
       <c r="I457" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J457" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K457" s="5"/>
       <c r="L457" s="4"/>
@@ -15603,29 +15602,29 @@
         <v>6</v>
       </c>
       <c r="B458" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C458" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D458" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E458" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F458" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C458" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="D458" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E458" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F458" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G458" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H458" s="2"/>
       <c r="I458" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J458" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K458" s="5"/>
       <c r="L458" s="4"/>
@@ -15635,99 +15634,35 @@
         <v>6</v>
       </c>
       <c r="B459" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C459" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="D459" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E459" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F459" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C459" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="D459" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E459" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F459" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="G459" s="4" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H459" s="2"/>
       <c r="I459" s="4" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="J459" s="4" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="K459" s="5"/>
       <c r="L459" s="4"/>
     </row>
-    <row r="460" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A460" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B460" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="C460" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="D460" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E460" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F460" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="G460" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="H460" s="2"/>
-      <c r="I460" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="J460" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="K460" s="5"/>
-      <c r="L460" s="4"/>
-    </row>
-    <row r="461" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A461" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B461" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="C461" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="D461" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E461" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="F461" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="G461" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="H461" s="2"/>
-      <c r="I461" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="J461" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="K461" s="5"/>
-      <c r="L461" s="4"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L461"/>
+  <autoFilter ref="A1:L459"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -15756,31 +15691,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15788,16 +15723,16 @@
         <v>0</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>4</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15815,7 +15750,7 @@
         <v>15</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15833,7 +15768,7 @@
         <v>278</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15851,7 +15786,7 @@
         <v>278</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15869,7 +15804,7 @@
         <v>341</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15877,17 +15812,17 @@
         <v>5</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>373</v>
+        <v>513</v>
       </c>
       <c r="C12" s="0" t="n">
         <f aca="false">COUNTIF('Disavow Review'!$A:$A,A12)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>278</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15895,58 +15830,58 @@
         <v>6</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C13" s="0" t="n">
         <f aca="false">COUNTIF('Disavow Review'!$A:$A,A13)</f>
         <v>117</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="17" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="C14" s="17" t="n">
         <f aca="false">SUM(C8:C13)</f>
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="0" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C16" s="0" t="n">
         <f aca="false">C14-C11</f>
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="0" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C17" s="0" t="n">
         <f aca="false">C14-C13</f>
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="0" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="C18" s="0" t="n">
         <f aca="false">C14-C11-C13</f>
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="0" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C20" s="0" t="n">
         <f aca="false">COUNTIF('Disavow Review'!$K:$K,"KEEP")</f>
@@ -15955,7 +15890,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="0" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C21" s="0" t="n">
         <f aca="false">COUNTIF('Disavow Review'!$K:$K,"DROP")</f>
@@ -15964,11 +15899,11 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="0" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="C22" s="0" t="n">
         <f aca="false">C14-C20-C21</f>
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15976,27 +15911,27 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="18" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="18" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="18" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16004,37 +15939,37 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="18" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="18" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="18" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="18" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="18" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="18" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16042,12 +15977,12 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="18" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="18" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
   </sheetData>

--- a/backlink-audit/disavow-review.xlsx
+++ b/backlink-audit/disavow-review.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Disavow Review'!$A$1:$L$459</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Disavow Review'!$A$1:$L$463</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3097" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3137" uniqueCount="555">
   <si>
     <t xml:space="preserve">Section</t>
   </si>
@@ -1145,6 +1145,48 @@
     <t xml:space="preserve">youtoo.in</t>
   </si>
   <si>
+    <t xml:space="preserve">Network D - compromised-host injection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beihaishitrade.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(a)+(b)+(c)+(d)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strong - newly found</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dofollow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same article.php script, identical nonsense title, client's own page titles as anchors injected into unrelated topics. One copy in a WordPress uploads dir = host compromise. Ahrefs flagged NONE of them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nextndt.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">matyesz.hu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendor path missed by anchor sweep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">backlinksolutions.info</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(b)+(d)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semrush</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is link-vendor sales copy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendor sales copy is in the URL path rather than the anchor, so the anchor-only sweep missed it.</t>
+  </si>
+  <si>
     <t xml:space="preserve">SEMRUSH-ONLY - Ahrefs never crawled</t>
   </si>
   <si>
@@ -1154,10 +1196,7 @@
     <t xml:space="preserve">(a)+(b)</t>
   </si>
   <si>
-    <t xml:space="preserve">REVIEW - single-source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Semrush</t>
+    <t xml:space="preserve">TIERED - see note</t>
   </si>
   <si>
     <t xml:space="preserve">Increase Google Visibility with High Quality Backlinks ngwindows.com</t>
@@ -1166,7 +1205,7 @@
     <t xml:space="preserve">1 dofollow</t>
   </si>
   <si>
-    <t xml:space="preserve">No Ahrefs corroboration possible (domain not in its index). No target_url column, so evidenced by anchor text only.</t>
+    <t xml:space="preserve">76 carry campaign ID 148096 in the path (structural, submit now); 16 share a byte-identical path (submit now); 25 are anchor-only - hold to 25 Oct.</t>
   </si>
   <si>
     <t xml:space="preserve">100ranking.link</t>
@@ -1547,7 +1586,7 @@
     <t xml:space="preserve">Status</t>
   </si>
   <si>
-    <t xml:space="preserve">NOT FINAL - see Verdict below</t>
+    <t xml:space="preserve">VERIFIED - all 462 checked entry-by-entry</t>
   </si>
   <si>
     <t xml:space="preserve">Name</t>
@@ -1562,25 +1601,25 @@
     <t xml:space="preserve">Submit as-is</t>
   </si>
   <si>
-    <t xml:space="preserve">REVIEW then decide - safe to drop</t>
+    <t xml:space="preserve">KEEP - verified exactly</t>
   </si>
   <si>
     <t xml:space="preserve">Auto-generated directory injection</t>
   </si>
   <si>
-    <t xml:space="preserve">REVIEW - weakest evidence</t>
+    <t xml:space="preserve">WITHDRAWN - false positives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier it: 92 now, 25 hold</t>
   </si>
   <si>
     <t xml:space="preserve">TOTAL</t>
   </si>
   <si>
-    <t xml:space="preserve">If you DROP Section 4 only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If you DROP Section 6 only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If you DROP both 4 and 6</t>
+    <t xml:space="preserve">Submit now (hold Section 6 anchor-only tier of 25)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If you also DROP Section 4</t>
   </si>
   <si>
     <t xml:space="preserve">Marked KEEP by reviewer</t>
@@ -1592,46 +1631,64 @@
     <t xml:space="preserve">Still unreviewed</t>
   </si>
   <si>
-    <t xml:space="preserve">VERDICT: not finally correct. Three things stand between this and submission:</t>
+    <t xml:space="preserve">VERIFICATION COMPLETE - four agents checked all entries against the raw exports.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REMOVED as false positives:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  whosmypro.com - a REAL directory. 72 distinct pages (not 133), 105-223 external links to</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    41-84 domains per page, real Georgia cities, standard directory CTA anchor. Decisively,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    72 rows target the CLIENT'S OWN Google Business Profile URL with the client's own UTM tags.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    It is a scraped GBP citation. Request listing removal instead - do NOT disavow.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  homeownerideas.com - real contractor directory. "Roswell New Mexico" is a city-name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    disambiguation bug, not fabricated geography. Anchor is a bare URL on all 4 rows.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REJECTED addition (checked and does not hold):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  newsblogsports.site - its anchor names SiteToSocial.com, a DIFFERENT client of the same</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    vendor. No client-naming anchor in either dataset. The /all/ path family is 22 hosts,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    all 22 already listed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STILL OUTSTANDING before upload:</t>
   </si>
   <si>
     <t xml:space="preserve">  1. GSC Manual Actions has never been checked. It gates whether to file at all.</t>
   </si>
   <si>
-    <t xml:space="preserve">  2. Section 6 (Semrush-only) is single-source: Ahrefs has never crawled those domains,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     and the Semrush export carries no target_url column, so routing is inferred from anchor text.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  3. Section 4 is a weaker motive tier - the operator sells domains rather than boosting this client.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What IS settled:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  - No entry uses Domain Rating, Authority Score, traffic, TLD, country or hosting as grounds.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  - Ahrefs spam flag is corroborating only, never a sole ground. Measured 3.0% over-firing;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    all 10 false positives were excluded by name.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  - Under-firing was the larger problem (10.6%); 17 Section 4 domains are included despite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Ahrefs NOT flagging them.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  - Where both tools see a domain they agree 31 of 31.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liveness caveat: no page was fetched at build time. Link status is as of each export date,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not today. The campaign was still adding links on 2026-10-06.</t>
+    <t xml:space="preserve">  2. Section 6 should be TIERED, not submitted or withheld as a block.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  3. ~20 further marketplace mirrors exist if Section 4 is kept - not added unilaterally.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A disavow filed for ngwindows.com CANNOT reach the ~2,587 links aimed at the seven redirect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shells. This file addresses campaign 148096 only; shell remediation is a separate track.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liveness: no page was fetched at build time. Status is as of each export date. 514 of 516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Section 1 rows are single-observation (first seen == last seen).</t>
   </si>
 </sst>
 </file>
@@ -1641,7 +1698,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1688,7 +1745,7 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1708,15 +1765,8 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1750,13 +1800,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFE699"/>
-        <bgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor rgb="FFFFE699"/>
+        <bgColor rgb="FFFFCC99"/>
       </patternFill>
     </fill>
   </fills>
@@ -1809,7 +1853,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1842,10 +1886,6 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1874,19 +1914,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1899,7 +1931,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1942,14 +1974,6 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FFFFE699"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -1974,8 +1998,8 @@
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF9C0006"/>
-      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF006100"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
@@ -2005,7 +2029,7 @@
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFC7CE"/>
+      <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -2211,7 +2235,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L459"/>
+  <dimension ref="A1:L463"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -11098,7 +11122,7 @@
       <c r="D317" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E317" s="7" t="s">
+      <c r="E317" s="2" t="s">
         <v>341</v>
       </c>
       <c r="F317" s="2" t="s">
@@ -11130,7 +11154,7 @@
       <c r="D318" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E318" s="7" t="s">
+      <c r="E318" s="2" t="s">
         <v>341</v>
       </c>
       <c r="F318" s="2" t="s">
@@ -11162,7 +11186,7 @@
       <c r="D319" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E319" s="7" t="s">
+      <c r="E319" s="2" t="s">
         <v>341</v>
       </c>
       <c r="F319" s="2" t="s">
@@ -11194,7 +11218,7 @@
       <c r="D320" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E320" s="7" t="s">
+      <c r="E320" s="2" t="s">
         <v>341</v>
       </c>
       <c r="F320" s="2" t="s">
@@ -11226,7 +11250,7 @@
       <c r="D321" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E321" s="7" t="s">
+      <c r="E321" s="2" t="s">
         <v>341</v>
       </c>
       <c r="F321" s="2" t="s">
@@ -11258,7 +11282,7 @@
       <c r="D322" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E322" s="7" t="s">
+      <c r="E322" s="2" t="s">
         <v>341</v>
       </c>
       <c r="F322" s="2" t="s">
@@ -11290,7 +11314,7 @@
       <c r="D323" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E323" s="7" t="s">
+      <c r="E323" s="2" t="s">
         <v>341</v>
       </c>
       <c r="F323" s="2" t="s">
@@ -11322,7 +11346,7 @@
       <c r="D324" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E324" s="7" t="s">
+      <c r="E324" s="2" t="s">
         <v>341</v>
       </c>
       <c r="F324" s="2" t="s">
@@ -11354,7 +11378,7 @@
       <c r="D325" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E325" s="7" t="s">
+      <c r="E325" s="2" t="s">
         <v>341</v>
       </c>
       <c r="F325" s="2" t="s">
@@ -11386,7 +11410,7 @@
       <c r="D326" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E326" s="7" t="s">
+      <c r="E326" s="2" t="s">
         <v>341</v>
       </c>
       <c r="F326" s="2" t="s">
@@ -11418,7 +11442,7 @@
       <c r="D327" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E327" s="7" t="s">
+      <c r="E327" s="2" t="s">
         <v>341</v>
       </c>
       <c r="F327" s="2" t="s">
@@ -11450,7 +11474,7 @@
       <c r="D328" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E328" s="7" t="s">
+      <c r="E328" s="2" t="s">
         <v>341</v>
       </c>
       <c r="F328" s="2" t="s">
@@ -11482,7 +11506,7 @@
       <c r="D329" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E329" s="7" t="s">
+      <c r="E329" s="2" t="s">
         <v>341</v>
       </c>
       <c r="F329" s="2" t="s">
@@ -11514,7 +11538,7 @@
       <c r="D330" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E330" s="7" t="s">
+      <c r="E330" s="2" t="s">
         <v>341</v>
       </c>
       <c r="F330" s="2" t="s">
@@ -11546,7 +11570,7 @@
       <c r="D331" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E331" s="7" t="s">
+      <c r="E331" s="2" t="s">
         <v>341</v>
       </c>
       <c r="F331" s="2" t="s">
@@ -11578,7 +11602,7 @@
       <c r="D332" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E332" s="7" t="s">
+      <c r="E332" s="2" t="s">
         <v>341</v>
       </c>
       <c r="F332" s="2" t="s">
@@ -11610,7 +11634,7 @@
       <c r="D333" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E333" s="7" t="s">
+      <c r="E333" s="2" t="s">
         <v>341</v>
       </c>
       <c r="F333" s="2" t="s">
@@ -11642,7 +11666,7 @@
       <c r="D334" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E334" s="7" t="s">
+      <c r="E334" s="2" t="s">
         <v>341</v>
       </c>
       <c r="F334" s="2" t="s">
@@ -11674,7 +11698,7 @@
       <c r="D335" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E335" s="7" t="s">
+      <c r="E335" s="2" t="s">
         <v>341</v>
       </c>
       <c r="F335" s="2" t="s">
@@ -11706,7 +11730,7 @@
       <c r="D336" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E336" s="7" t="s">
+      <c r="E336" s="2" t="s">
         <v>341</v>
       </c>
       <c r="F336" s="2" t="s">
@@ -11738,7 +11762,7 @@
       <c r="D337" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E337" s="7" t="s">
+      <c r="E337" s="2" t="s">
         <v>341</v>
       </c>
       <c r="F337" s="2" t="s">
@@ -11770,7 +11794,7 @@
       <c r="D338" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E338" s="7" t="s">
+      <c r="E338" s="2" t="s">
         <v>341</v>
       </c>
       <c r="F338" s="2" t="s">
@@ -11802,7 +11826,7 @@
       <c r="D339" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E339" s="7" t="s">
+      <c r="E339" s="2" t="s">
         <v>341</v>
       </c>
       <c r="F339" s="2" t="s">
@@ -11834,7 +11858,7 @@
       <c r="D340" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E340" s="7" t="s">
+      <c r="E340" s="2" t="s">
         <v>341</v>
       </c>
       <c r="F340" s="2" t="s">
@@ -11866,7 +11890,7 @@
       <c r="D341" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E341" s="7" t="s">
+      <c r="E341" s="2" t="s">
         <v>341</v>
       </c>
       <c r="F341" s="2" t="s">
@@ -11898,7 +11922,7 @@
       <c r="D342" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E342" s="7" t="s">
+      <c r="E342" s="2" t="s">
         <v>341</v>
       </c>
       <c r="F342" s="2" t="s">
@@ -11917,9 +11941,9 @@
       <c r="K342" s="5"/>
       <c r="L342" s="4"/>
     </row>
-    <row r="343" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="343" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>373</v>
@@ -11930,3739 +11954,3861 @@
       <c r="D343" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="E343" s="8" t="s">
+      <c r="E343" s="6" t="s">
         <v>376</v>
       </c>
       <c r="F343" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="G343" s="4" t="s">
-        <v>378</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G343" s="4"/>
       <c r="H343" s="2"/>
       <c r="I343" s="4" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="J343" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="K343" s="5"/>
       <c r="L343" s="4"/>
     </row>
-    <row r="344" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="344" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>373</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D344" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="E344" s="8" t="s">
+      <c r="E344" s="6" t="s">
         <v>376</v>
       </c>
       <c r="F344" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="G344" s="4" t="s">
-        <v>378</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G344" s="4"/>
       <c r="H344" s="2"/>
       <c r="I344" s="4" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="J344" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="K344" s="5"/>
       <c r="L344" s="4"/>
     </row>
-    <row r="345" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="345" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B345" s="2" t="s">
         <v>373</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D345" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="E345" s="8" t="s">
+      <c r="E345" s="6" t="s">
         <v>376</v>
       </c>
       <c r="F345" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="G345" s="4" t="s">
-        <v>378</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G345" s="4"/>
       <c r="H345" s="2"/>
       <c r="I345" s="4" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="J345" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="K345" s="5"/>
       <c r="L345" s="4"/>
     </row>
     <row r="346" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="C346" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="D346" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E346" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="F346" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="D346" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E346" s="8" t="s">
-        <v>376</v>
-      </c>
-      <c r="F346" s="2" t="s">
+      <c r="G346" s="4"/>
+      <c r="H346" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="I346" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="G346" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="H346" s="2"/>
-      <c r="I346" s="4" t="s">
-        <v>379</v>
-      </c>
       <c r="J346" s="4" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="K346" s="5"/>
       <c r="L346" s="4"/>
     </row>
-    <row r="347" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="347" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E347" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E347" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F347" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G347" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H347" s="2"/>
       <c r="I347" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J347" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K347" s="5"/>
       <c r="L347" s="4"/>
     </row>
-    <row r="348" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="348" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E348" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E348" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F348" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G348" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="H348" s="2"/>
       <c r="I348" s="4" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="J348" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K348" s="5"/>
       <c r="L348" s="4"/>
     </row>
-    <row r="349" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="349" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E349" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E349" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F349" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G349" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H349" s="2"/>
       <c r="I349" s="4" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="J349" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K349" s="5"/>
       <c r="L349" s="4"/>
     </row>
-    <row r="350" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="350" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C350" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D350" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="D350" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E350" s="8" t="s">
-        <v>376</v>
+      <c r="E350" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F350" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G350" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H350" s="2"/>
       <c r="I350" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J350" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K350" s="5"/>
       <c r="L350" s="4"/>
     </row>
-    <row r="351" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="351" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C351" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D351" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="E351" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="F351" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="G351" s="4" t="s">
         <v>391</v>
-      </c>
-      <c r="D351" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E351" s="8" t="s">
-        <v>376</v>
-      </c>
-      <c r="F351" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="G351" s="4" t="s">
-        <v>387</v>
       </c>
       <c r="H351" s="2"/>
       <c r="I351" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J351" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K351" s="5"/>
       <c r="L351" s="4"/>
     </row>
-    <row r="352" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="352" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E352" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E352" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F352" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G352" s="4" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="H352" s="2"/>
       <c r="I352" s="4" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="J352" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K352" s="5"/>
       <c r="L352" s="4"/>
     </row>
-    <row r="353" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="353" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E353" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E353" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F353" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G353" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H353" s="2"/>
       <c r="I353" s="4" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="J353" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K353" s="5"/>
       <c r="L353" s="4"/>
     </row>
-    <row r="354" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="354" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E354" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E354" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F354" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G354" s="4" t="s">
-        <v>378</v>
+        <v>403</v>
       </c>
       <c r="H354" s="2"/>
       <c r="I354" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J354" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K354" s="5"/>
       <c r="L354" s="4"/>
     </row>
-    <row r="355" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="355" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E355" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E355" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F355" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G355" s="4" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="H355" s="2"/>
       <c r="I355" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J355" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K355" s="5"/>
       <c r="L355" s="4"/>
     </row>
-    <row r="356" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="356" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E356" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E356" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F356" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G356" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H356" s="2"/>
       <c r="I356" s="4" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="J356" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K356" s="5"/>
       <c r="L356" s="4"/>
     </row>
-    <row r="357" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="357" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E357" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E357" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F357" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G357" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H357" s="2"/>
       <c r="I357" s="4" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="J357" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K357" s="5"/>
       <c r="L357" s="4"/>
     </row>
-    <row r="358" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="358" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E358" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E358" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F358" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G358" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H358" s="2"/>
       <c r="I358" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J358" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K358" s="5"/>
       <c r="L358" s="4"/>
     </row>
-    <row r="359" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="359" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E359" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E359" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F359" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G359" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H359" s="2"/>
       <c r="I359" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J359" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K359" s="5"/>
       <c r="L359" s="4"/>
     </row>
-    <row r="360" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="360" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="D360" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E360" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E360" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F360" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G360" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H360" s="2"/>
       <c r="I360" s="4" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="J360" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K360" s="5"/>
       <c r="L360" s="4"/>
     </row>
-    <row r="361" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="361" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="D361" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E361" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E361" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F361" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G361" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H361" s="2"/>
       <c r="I361" s="4" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="J361" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K361" s="5"/>
       <c r="L361" s="4"/>
     </row>
-    <row r="362" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="362" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="D362" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E362" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E362" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F362" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G362" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H362" s="2"/>
       <c r="I362" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J362" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K362" s="5"/>
       <c r="L362" s="4"/>
     </row>
-    <row r="363" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="363" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="D363" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E363" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E363" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F363" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G363" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H363" s="2"/>
       <c r="I363" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J363" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K363" s="5"/>
       <c r="L363" s="4"/>
     </row>
-    <row r="364" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="364" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="D364" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E364" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E364" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F364" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G364" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H364" s="2"/>
       <c r="I364" s="4" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="J364" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K364" s="5"/>
       <c r="L364" s="4"/>
     </row>
-    <row r="365" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="365" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E365" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E365" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F365" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G365" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H365" s="2"/>
       <c r="I365" s="4" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="J365" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K365" s="5"/>
       <c r="L365" s="4"/>
     </row>
-    <row r="366" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="366" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E366" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E366" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F366" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G366" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H366" s="2"/>
       <c r="I366" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J366" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K366" s="5"/>
       <c r="L366" s="4"/>
     </row>
-    <row r="367" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="367" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E367" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E367" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F367" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G367" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H367" s="2"/>
       <c r="I367" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J367" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K367" s="5"/>
       <c r="L367" s="4"/>
     </row>
-    <row r="368" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="368" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="D368" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E368" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E368" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F368" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G368" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H368" s="2"/>
       <c r="I368" s="4" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="J368" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K368" s="5"/>
       <c r="L368" s="4"/>
     </row>
-    <row r="369" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="369" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="D369" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E369" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E369" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F369" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G369" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="H369" s="2"/>
       <c r="I369" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J369" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K369" s="5"/>
       <c r="L369" s="4"/>
     </row>
-    <row r="370" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="370" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="D370" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E370" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E370" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F370" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G370" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H370" s="2"/>
       <c r="I370" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J370" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K370" s="5"/>
       <c r="L370" s="4"/>
     </row>
-    <row r="371" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="371" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="D371" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E371" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E371" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F371" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G371" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="H371" s="2"/>
       <c r="I371" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J371" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K371" s="5"/>
       <c r="L371" s="4"/>
     </row>
-    <row r="372" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="372" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="D372" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E372" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E372" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F372" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G372" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H372" s="2"/>
       <c r="I372" s="4" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="J372" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K372" s="5"/>
       <c r="L372" s="4"/>
     </row>
-    <row r="373" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="373" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="D373" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E373" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E373" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F373" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G373" s="4" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="H373" s="2"/>
       <c r="I373" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J373" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K373" s="5"/>
       <c r="L373" s="4"/>
     </row>
-    <row r="374" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="374" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="D374" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E374" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E374" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F374" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G374" s="4" t="s">
-        <v>378</v>
+        <v>403</v>
       </c>
       <c r="H374" s="2"/>
       <c r="I374" s="4" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="J374" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K374" s="5"/>
       <c r="L374" s="4"/>
     </row>
-    <row r="375" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="375" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="D375" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E375" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E375" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F375" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G375" s="4" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="H375" s="2"/>
       <c r="I375" s="4" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="J375" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K375" s="5"/>
       <c r="L375" s="4"/>
     </row>
-    <row r="376" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="376" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="D376" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E376" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E376" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F376" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G376" s="4" t="s">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="H376" s="2"/>
       <c r="I376" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J376" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K376" s="5"/>
       <c r="L376" s="4"/>
     </row>
-    <row r="377" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="377" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="D377" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E377" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E377" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F377" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G377" s="4" t="s">
-        <v>378</v>
+        <v>403</v>
       </c>
       <c r="H377" s="2"/>
       <c r="I377" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J377" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K377" s="5"/>
       <c r="L377" s="4"/>
     </row>
-    <row r="378" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="378" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="D378" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E378" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E378" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F378" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G378" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H378" s="2"/>
       <c r="I378" s="4" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="J378" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K378" s="5"/>
       <c r="L378" s="4"/>
     </row>
-    <row r="379" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="379" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="D379" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E379" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E379" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F379" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G379" s="4" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="H379" s="2"/>
       <c r="I379" s="4" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="J379" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K379" s="5"/>
       <c r="L379" s="4"/>
     </row>
-    <row r="380" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="380" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="D380" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E380" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E380" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F380" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G380" s="4" t="s">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="H380" s="2"/>
       <c r="I380" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J380" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K380" s="5"/>
       <c r="L380" s="4"/>
     </row>
-    <row r="381" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="381" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="D381" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E381" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E381" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F381" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G381" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H381" s="2"/>
       <c r="I381" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J381" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K381" s="5"/>
       <c r="L381" s="4"/>
     </row>
-    <row r="382" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="382" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="D382" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E382" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E382" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F382" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G382" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="H382" s="2"/>
       <c r="I382" s="4" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="J382" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K382" s="5"/>
       <c r="L382" s="4"/>
     </row>
-    <row r="383" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="383" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="D383" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E383" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E383" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F383" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G383" s="4" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="H383" s="2"/>
       <c r="I383" s="4" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="J383" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K383" s="5"/>
       <c r="L383" s="4"/>
     </row>
-    <row r="384" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="384" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="D384" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E384" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E384" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F384" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G384" s="4" t="s">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="H384" s="2"/>
       <c r="I384" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J384" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K384" s="5"/>
       <c r="L384" s="4"/>
     </row>
-    <row r="385" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="385" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="D385" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E385" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E385" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F385" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G385" s="4" t="s">
-        <v>387</v>
+        <v>403</v>
       </c>
       <c r="H385" s="2"/>
       <c r="I385" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J385" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K385" s="5"/>
       <c r="L385" s="4"/>
     </row>
-    <row r="386" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="386" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="D386" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E386" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E386" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F386" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G386" s="4" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="H386" s="2"/>
       <c r="I386" s="4" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="J386" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K386" s="5"/>
       <c r="L386" s="4"/>
     </row>
-    <row r="387" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="387" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="D387" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E387" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E387" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F387" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G387" s="4" t="s">
-        <v>387</v>
+        <v>403</v>
       </c>
       <c r="H387" s="2"/>
       <c r="I387" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J387" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K387" s="5"/>
       <c r="L387" s="4"/>
     </row>
-    <row r="388" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="388" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E388" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E388" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F388" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G388" s="4" t="s">
-        <v>387</v>
+        <v>403</v>
       </c>
       <c r="H388" s="2"/>
       <c r="I388" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J388" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K388" s="5"/>
       <c r="L388" s="4"/>
     </row>
-    <row r="389" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="389" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E389" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E389" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F389" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G389" s="4" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="H389" s="2"/>
       <c r="I389" s="4" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="J389" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K389" s="5"/>
       <c r="L389" s="4"/>
     </row>
-    <row r="390" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="390" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E390" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E390" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F390" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G390" s="4" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="H390" s="2"/>
       <c r="I390" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J390" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K390" s="5"/>
       <c r="L390" s="4"/>
     </row>
-    <row r="391" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="391" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E391" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E391" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F391" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G391" s="4" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="H391" s="2"/>
       <c r="I391" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J391" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K391" s="5"/>
       <c r="L391" s="4"/>
     </row>
-    <row r="392" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="392" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E392" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E392" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F392" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G392" s="4" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="H392" s="2"/>
       <c r="I392" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J392" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K392" s="5"/>
       <c r="L392" s="4"/>
     </row>
-    <row r="393" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="393" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E393" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E393" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F393" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G393" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H393" s="2"/>
       <c r="I393" s="4" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="J393" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K393" s="5"/>
       <c r="L393" s="4"/>
     </row>
-    <row r="394" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="394" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A394" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E394" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E394" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F394" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G394" s="4" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="H394" s="2"/>
       <c r="I394" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J394" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K394" s="5"/>
       <c r="L394" s="4"/>
     </row>
-    <row r="395" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="395" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="D395" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E395" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E395" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F395" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G395" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H395" s="2"/>
       <c r="I395" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J395" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K395" s="5"/>
       <c r="L395" s="4"/>
     </row>
-    <row r="396" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="396" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A396" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E396" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E396" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F396" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G396" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H396" s="2"/>
       <c r="I396" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J396" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K396" s="5"/>
       <c r="L396" s="4"/>
     </row>
-    <row r="397" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="397" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="D397" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E397" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E397" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F397" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G397" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H397" s="2"/>
       <c r="I397" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J397" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K397" s="5"/>
       <c r="L397" s="4"/>
     </row>
-    <row r="398" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="398" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="D398" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E398" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E398" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F398" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G398" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H398" s="2"/>
       <c r="I398" s="4" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="J398" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K398" s="5"/>
       <c r="L398" s="4"/>
     </row>
-    <row r="399" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="399" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="D399" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E399" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E399" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F399" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G399" s="4" t="s">
-        <v>378</v>
+        <v>403</v>
       </c>
       <c r="H399" s="2"/>
       <c r="I399" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J399" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K399" s="5"/>
       <c r="L399" s="4"/>
     </row>
-    <row r="400" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="400" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="D400" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E400" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E400" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F400" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G400" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H400" s="2"/>
       <c r="I400" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J400" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K400" s="5"/>
       <c r="L400" s="4"/>
     </row>
-    <row r="401" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="401" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="D401" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E401" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E401" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F401" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G401" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H401" s="2"/>
       <c r="I401" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J401" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K401" s="5"/>
       <c r="L401" s="4"/>
     </row>
-    <row r="402" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="402" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E402" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E402" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F402" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G402" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H402" s="2"/>
       <c r="I402" s="4" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="J402" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K402" s="5"/>
       <c r="L402" s="4"/>
     </row>
-    <row r="403" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="403" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="D403" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E403" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E403" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F403" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G403" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H403" s="2"/>
       <c r="I403" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J403" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K403" s="5"/>
       <c r="L403" s="4"/>
     </row>
-    <row r="404" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="404" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="D404" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E404" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E404" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F404" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G404" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="H404" s="2"/>
       <c r="I404" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J404" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K404" s="5"/>
       <c r="L404" s="4"/>
     </row>
-    <row r="405" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="405" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="D405" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E405" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E405" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F405" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G405" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H405" s="2"/>
       <c r="I405" s="4" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="J405" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K405" s="5"/>
       <c r="L405" s="4"/>
     </row>
-    <row r="406" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="406" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="D406" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E406" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E406" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F406" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G406" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H406" s="2"/>
       <c r="I406" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J406" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K406" s="5"/>
       <c r="L406" s="4"/>
     </row>
-    <row r="407" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="407" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="D407" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E407" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E407" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F407" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G407" s="4" t="s">
-        <v>387</v>
+        <v>403</v>
       </c>
       <c r="H407" s="2"/>
       <c r="I407" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J407" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K407" s="5"/>
       <c r="L407" s="4"/>
     </row>
-    <row r="408" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="408" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A408" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="D408" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E408" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E408" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F408" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G408" s="4" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="H408" s="2"/>
       <c r="I408" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J408" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K408" s="5"/>
       <c r="L408" s="4"/>
     </row>
-    <row r="409" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="409" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="D409" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E409" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E409" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F409" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G409" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H409" s="2"/>
       <c r="I409" s="4" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="J409" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K409" s="5"/>
       <c r="L409" s="4"/>
     </row>
-    <row r="410" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="410" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="D410" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E410" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E410" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F410" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G410" s="4" t="s">
-        <v>378</v>
+        <v>403</v>
       </c>
       <c r="H410" s="2"/>
       <c r="I410" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J410" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K410" s="5"/>
       <c r="L410" s="4"/>
     </row>
-    <row r="411" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="411" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="D411" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E411" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E411" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F411" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G411" s="4" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="H411" s="2"/>
       <c r="I411" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J411" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K411" s="5"/>
       <c r="L411" s="4"/>
     </row>
-    <row r="412" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="412" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="D412" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E412" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E412" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F412" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G412" s="4" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="H412" s="2"/>
       <c r="I412" s="4" t="s">
-        <v>453</v>
+        <v>392</v>
       </c>
       <c r="J412" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K412" s="5"/>
       <c r="L412" s="4"/>
     </row>
-    <row r="413" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="413" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="D413" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E413" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E413" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F413" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G413" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="H413" s="2"/>
       <c r="I413" s="4" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="J413" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K413" s="5"/>
       <c r="L413" s="4"/>
     </row>
-    <row r="414" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="414" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="D414" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E414" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E414" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F414" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G414" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="H414" s="2"/>
       <c r="I414" s="4" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="J414" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K414" s="5"/>
       <c r="L414" s="4"/>
     </row>
-    <row r="415" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="415" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="D415" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E415" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E415" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F415" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G415" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H415" s="2"/>
       <c r="I415" s="4" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="J415" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K415" s="5"/>
       <c r="L415" s="4"/>
     </row>
-    <row r="416" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="416" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="D416" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E416" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E416" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F416" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G416" s="4" t="s">
-        <v>378</v>
+        <v>403</v>
       </c>
       <c r="H416" s="2"/>
       <c r="I416" s="4" t="s">
-        <v>382</v>
+        <v>466</v>
       </c>
       <c r="J416" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K416" s="5"/>
       <c r="L416" s="4"/>
     </row>
-    <row r="417" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="417" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="D417" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E417" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E417" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F417" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G417" s="4" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="H417" s="2"/>
       <c r="I417" s="4" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="J417" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K417" s="5"/>
       <c r="L417" s="4"/>
     </row>
-    <row r="418" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="418" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="D418" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E418" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E418" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F418" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G418" s="4" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="H418" s="2"/>
       <c r="I418" s="4" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="J418" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K418" s="5"/>
       <c r="L418" s="4"/>
     </row>
-    <row r="419" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="419" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="D419" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E419" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E419" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F419" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G419" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H419" s="2"/>
       <c r="I419" s="4" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="J419" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K419" s="5"/>
       <c r="L419" s="4"/>
     </row>
-    <row r="420" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="420" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="D420" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E420" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E420" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F420" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G420" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H420" s="2"/>
       <c r="I420" s="4" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="J420" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K420" s="5"/>
       <c r="L420" s="4"/>
     </row>
-    <row r="421" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="421" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A421" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="D421" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E421" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E421" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F421" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G421" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H421" s="2"/>
       <c r="I421" s="4" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="J421" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K421" s="5"/>
       <c r="L421" s="4"/>
     </row>
-    <row r="422" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="422" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="D422" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E422" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E422" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F422" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G422" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="H422" s="2"/>
       <c r="I422" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J422" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K422" s="5"/>
       <c r="L422" s="4"/>
     </row>
-    <row r="423" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="423" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="D423" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E423" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E423" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F423" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G423" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H423" s="2"/>
       <c r="I423" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J423" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K423" s="5"/>
       <c r="L423" s="4"/>
     </row>
-    <row r="424" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="424" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="D424" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E424" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E424" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F424" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G424" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="H424" s="2"/>
       <c r="I424" s="4" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="J424" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K424" s="5"/>
       <c r="L424" s="4"/>
     </row>
-    <row r="425" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="425" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="D425" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E425" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E425" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F425" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G425" s="4" t="s">
-        <v>378</v>
+        <v>403</v>
       </c>
       <c r="H425" s="2"/>
       <c r="I425" s="4" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="J425" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K425" s="5"/>
       <c r="L425" s="4"/>
     </row>
-    <row r="426" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="426" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="D426" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E426" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E426" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F426" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G426" s="4" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="H426" s="2"/>
       <c r="I426" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J426" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K426" s="5"/>
       <c r="L426" s="4"/>
     </row>
-    <row r="427" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="427" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="D427" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E427" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E427" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F427" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G427" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="H427" s="2"/>
       <c r="I427" s="4" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="J427" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K427" s="5"/>
       <c r="L427" s="4"/>
     </row>
-    <row r="428" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="428" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="D428" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E428" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E428" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F428" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G428" s="4" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="H428" s="2"/>
       <c r="I428" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J428" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K428" s="5"/>
       <c r="L428" s="4"/>
     </row>
-    <row r="429" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="429" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="D429" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E429" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E429" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F429" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G429" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H429" s="2"/>
       <c r="I429" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J429" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K429" s="5"/>
       <c r="L429" s="4"/>
     </row>
-    <row r="430" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="430" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="D430" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E430" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E430" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F430" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G430" s="4" t="s">
-        <v>387</v>
+        <v>403</v>
       </c>
       <c r="H430" s="2"/>
       <c r="I430" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J430" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K430" s="5"/>
       <c r="L430" s="4"/>
     </row>
-    <row r="431" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="431" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="D431" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E431" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E431" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F431" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G431" s="4" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="H431" s="2"/>
       <c r="I431" s="4" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="J431" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K431" s="5"/>
       <c r="L431" s="4"/>
     </row>
-    <row r="432" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="432" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="D432" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E432" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E432" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F432" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G432" s="4" t="s">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="H432" s="2"/>
       <c r="I432" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J432" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K432" s="5"/>
       <c r="L432" s="4"/>
     </row>
-    <row r="433" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="433" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E433" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E433" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F433" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G433" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H433" s="2"/>
       <c r="I433" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J433" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K433" s="5"/>
       <c r="L433" s="4"/>
     </row>
-    <row r="434" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="434" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A434" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E434" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E434" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F434" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G434" s="4" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="H434" s="2"/>
       <c r="I434" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J434" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K434" s="5"/>
       <c r="L434" s="4"/>
     </row>
-    <row r="435" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="435" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A435" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E435" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E435" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F435" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G435" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H435" s="2"/>
       <c r="I435" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J435" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K435" s="5"/>
       <c r="L435" s="4"/>
     </row>
-    <row r="436" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="436" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E436" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E436" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F436" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G436" s="4" t="s">
-        <v>387</v>
+        <v>403</v>
       </c>
       <c r="H436" s="2"/>
       <c r="I436" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J436" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K436" s="5"/>
       <c r="L436" s="4"/>
     </row>
-    <row r="437" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="437" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E437" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E437" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F437" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G437" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H437" s="2"/>
       <c r="I437" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J437" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K437" s="5"/>
       <c r="L437" s="4"/>
     </row>
-    <row r="438" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="438" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A438" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E438" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E438" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F438" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G438" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H438" s="2"/>
       <c r="I438" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J438" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K438" s="5"/>
       <c r="L438" s="4"/>
     </row>
-    <row r="439" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="439" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E439" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E439" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F439" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G439" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H439" s="2"/>
       <c r="I439" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J439" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K439" s="5"/>
       <c r="L439" s="4"/>
     </row>
-    <row r="440" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="440" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C440" s="2" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E440" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E440" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F440" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G440" s="4" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="H440" s="2"/>
       <c r="I440" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J440" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K440" s="5"/>
       <c r="L440" s="4"/>
     </row>
-    <row r="441" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="441" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E441" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E441" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F441" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G441" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H441" s="2"/>
       <c r="I441" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J441" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K441" s="5"/>
       <c r="L441" s="4"/>
     </row>
-    <row r="442" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="442" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B442" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E442" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E442" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F442" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G442" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H442" s="2"/>
       <c r="I442" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J442" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K442" s="5"/>
       <c r="L442" s="4"/>
     </row>
-    <row r="443" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="443" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E443" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E443" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F443" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G443" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H443" s="2"/>
       <c r="I443" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J443" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K443" s="5"/>
       <c r="L443" s="4"/>
     </row>
-    <row r="444" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="444" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E444" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E444" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F444" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G444" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H444" s="2"/>
       <c r="I444" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J444" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K444" s="5"/>
       <c r="L444" s="4"/>
     </row>
-    <row r="445" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="445" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="D445" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E445" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E445" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F445" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G445" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H445" s="2"/>
       <c r="I445" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J445" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K445" s="5"/>
       <c r="L445" s="4"/>
     </row>
-    <row r="446" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="446" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C446" s="2" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="D446" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E446" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E446" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F446" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G446" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H446" s="2"/>
       <c r="I446" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J446" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K446" s="5"/>
       <c r="L446" s="4"/>
     </row>
-    <row r="447" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="447" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A447" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C447" s="2" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E447" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E447" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F447" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G447" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H447" s="2"/>
       <c r="I447" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J447" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K447" s="5"/>
       <c r="L447" s="4"/>
     </row>
-    <row r="448" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="448" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C448" s="2" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E448" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E448" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F448" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G448" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H448" s="2"/>
       <c r="I448" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J448" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K448" s="5"/>
       <c r="L448" s="4"/>
     </row>
-    <row r="449" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="449" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E449" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E449" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F449" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G449" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H449" s="2"/>
       <c r="I449" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J449" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K449" s="5"/>
       <c r="L449" s="4"/>
     </row>
-    <row r="450" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="450" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E450" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E450" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F450" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G450" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H450" s="2"/>
       <c r="I450" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J450" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K450" s="5"/>
       <c r="L450" s="4"/>
     </row>
-    <row r="451" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="451" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E451" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E451" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F451" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G451" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H451" s="2"/>
       <c r="I451" s="4" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="J451" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K451" s="5"/>
       <c r="L451" s="4"/>
     </row>
-    <row r="452" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="452" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A452" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E452" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E452" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F452" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G452" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="H452" s="2"/>
       <c r="I452" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J452" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K452" s="5"/>
       <c r="L452" s="4"/>
     </row>
-    <row r="453" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="453" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A453" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E453" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E453" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F453" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G453" s="4" t="s">
-        <v>378</v>
+        <v>403</v>
       </c>
       <c r="H453" s="2"/>
       <c r="I453" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J453" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K453" s="5"/>
       <c r="L453" s="4"/>
     </row>
-    <row r="454" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="454" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C454" s="2" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E454" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E454" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F454" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G454" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H454" s="2"/>
       <c r="I454" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J454" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K454" s="5"/>
       <c r="L454" s="4"/>
     </row>
-    <row r="455" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="455" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E455" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E455" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F455" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G455" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H455" s="2"/>
       <c r="I455" s="4" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="J455" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K455" s="5"/>
       <c r="L455" s="4"/>
     </row>
-    <row r="456" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="456" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E456" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E456" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F456" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G456" s="4" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="H456" s="2"/>
       <c r="I456" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J456" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K456" s="5"/>
       <c r="L456" s="4"/>
     </row>
-    <row r="457" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="457" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C457" s="2" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E457" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E457" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F457" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G457" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H457" s="2"/>
       <c r="I457" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J457" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K457" s="5"/>
       <c r="L457" s="4"/>
     </row>
-    <row r="458" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="458" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="D458" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E458" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E458" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F458" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G458" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H458" s="2"/>
       <c r="I458" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J458" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K458" s="5"/>
       <c r="L458" s="4"/>
     </row>
-    <row r="459" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="459" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C459" s="2" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="D459" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E459" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
+      </c>
+      <c r="E459" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="F459" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G459" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H459" s="2"/>
       <c r="I459" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="J459" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="K459" s="5"/>
       <c r="L459" s="4"/>
     </row>
+    <row r="460" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A460" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B460" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C460" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="D460" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="E460" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="F460" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="G460" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="H460" s="2"/>
+      <c r="I460" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="J460" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="K460" s="5"/>
+      <c r="L460" s="4"/>
+    </row>
+    <row r="461" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A461" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B461" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C461" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="D461" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="E461" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="F461" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="G461" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="H461" s="2"/>
+      <c r="I461" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="J461" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="K461" s="5"/>
+      <c r="L461" s="4"/>
+    </row>
+    <row r="462" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A462" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B462" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C462" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="D462" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="E462" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="F462" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="G462" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="H462" s="2"/>
+      <c r="I462" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="J462" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="K462" s="5"/>
+      <c r="L462" s="4"/>
+    </row>
+    <row r="463" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A463" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B463" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C463" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="D463" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="E463" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="F463" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="G463" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="H463" s="2"/>
+      <c r="I463" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="J463" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="K463" s="5"/>
+      <c r="L463" s="4"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L459"/>
+  <autoFilter ref="A1:L463"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -15679,7 +15825,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -15690,49 +15836,49 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
-        <v>501</v>
+      <c r="A1" s="8" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>502</v>
+        <v>515</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>503</v>
+        <v>516</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>504</v>
+        <v>517</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>505</v>
+        <v>518</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>507</v>
+        <v>519</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="11" t="s">
-        <v>508</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>509</v>
-      </c>
-      <c r="D7" s="11" t="s">
+      <c r="B7" s="10" t="s">
+        <v>521</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>522</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="11" t="s">
-        <v>510</v>
+      <c r="E7" s="10" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15746,11 +15892,11 @@
         <f aca="false">COUNTIF('Disavow Review'!$A:$A,A8)</f>
         <v>258</v>
       </c>
-      <c r="D8" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>511</v>
+      <c r="D8" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15764,11 +15910,11 @@
         <f aca="false">COUNTIF('Disavow Review'!$A:$A,A9)</f>
         <v>43</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="E9" s="13" t="s">
-        <v>511</v>
+      <c r="E9" s="12" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15782,11 +15928,11 @@
         <f aca="false">COUNTIF('Disavow Review'!$A:$A,A10)</f>
         <v>14</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="E10" s="13" t="s">
-        <v>511</v>
+      <c r="E10" s="12" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15800,11 +15946,11 @@
         <f aca="false">COUNTIF('Disavow Review'!$A:$A,A11)</f>
         <v>26</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="0" t="s">
         <v>341</v>
       </c>
-      <c r="E11" s="13" t="s">
-        <v>512</v>
+      <c r="E11" s="0" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15812,17 +15958,17 @@
         <v>5</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="C12" s="0" t="n">
         <f aca="false">COUNTIF('Disavow Review'!$A:$A,A12)</f>
         <v>0</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="E12" s="13" t="s">
-        <v>511</v>
+      <c r="E12" s="12" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15830,159 +15976,225 @@
         <v>6</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C13" s="0" t="n">
         <f aca="false">COUNTIF('Disavow Review'!$A:$A,A13)</f>
         <v>117</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="14" t="s">
+        <v>390</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>373</v>
+      </c>
+      <c r="C14" s="0" t="n">
+        <f aca="false">COUNTIF('Disavow Review'!$A:$A,A14)</f>
+        <v>3</v>
+      </c>
+      <c r="D14" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="E13" s="13" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="17" t="s">
-        <v>515</v>
-      </c>
-      <c r="C14" s="17" t="n">
-        <f aca="false">SUM(C8:C13)</f>
-        <v>458</v>
+      <c r="E14" s="12" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>381</v>
+      </c>
+      <c r="C15" s="0" t="n">
+        <f aca="false">COUNTIF('Disavow Review'!$A:$A,A15)</f>
+        <v>1</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0" t="s">
-        <v>516</v>
-      </c>
-      <c r="C16" s="0" t="n">
-        <f aca="false">C14-C11</f>
-        <v>432</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0" t="s">
-        <v>517</v>
-      </c>
-      <c r="C17" s="0" t="n">
-        <f aca="false">C14-C13</f>
-        <v>341</v>
+      <c r="B16" s="15" t="s">
+        <v>529</v>
+      </c>
+      <c r="C16" s="15" t="n">
+        <f aca="false">SUM(C8:C15)</f>
+        <v>462</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="0" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="C18" s="0" t="n">
-        <f aca="false">C14-C11-C13</f>
-        <v>315</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="0" t="s">
-        <v>519</v>
-      </c>
-      <c r="C20" s="0" t="n">
+        <f aca="false">C16-25</f>
+        <v>437</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="0" t="s">
+        <v>531</v>
+      </c>
+      <c r="C19" s="0" t="n">
+        <f aca="false">C16-25-C11</f>
+        <v>411</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="0" t="s">
+        <v>532</v>
+      </c>
+      <c r="C22" s="0" t="n">
         <f aca="false">COUNTIF('Disavow Review'!$K:$K,"KEEP")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="0" t="s">
-        <v>520</v>
-      </c>
-      <c r="C21" s="0" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="0" t="s">
+        <v>533</v>
+      </c>
+      <c r="C23" s="0" t="n">
         <f aca="false">COUNTIF('Disavow Review'!$K:$K,"DROP")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="0" t="s">
-        <v>521</v>
-      </c>
-      <c r="C22" s="0" t="n">
-        <f aca="false">C14-C20-C21</f>
-        <v>458</v>
-      </c>
-    </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="18"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19" t="s">
-        <v>522</v>
+      <c r="B24" s="0" t="s">
+        <v>534</v>
+      </c>
+      <c r="C24" s="0" t="n">
+        <f aca="false">C16-C22-C23</f>
+        <v>462</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="18" t="s">
-        <v>523</v>
-      </c>
+      <c r="A26" s="16"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="18" t="s">
-        <v>524</v>
+      <c r="A27" s="16" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18" t="s">
-        <v>525</v>
-      </c>
+      <c r="A28" s="16"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18" t="s">
-        <v>526</v>
+      <c r="A29" s="16" t="s">
+        <v>536</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="18"/>
+      <c r="A30" s="16" t="s">
+        <v>537</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="19" t="s">
-        <v>527</v>
+      <c r="A31" s="16" t="s">
+        <v>538</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18" t="s">
-        <v>528</v>
+      <c r="A32" s="16" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="18" t="s">
-        <v>529</v>
+      <c r="A33" s="16" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="18" t="s">
-        <v>530</v>
+      <c r="A34" s="16" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="18" t="s">
-        <v>531</v>
+      <c r="A35" s="16" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="18" t="s">
-        <v>532</v>
-      </c>
+      <c r="A36" s="16"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="18" t="s">
-        <v>533</v>
+      <c r="A37" s="16" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="18"/>
+      <c r="A38" s="16" t="s">
+        <v>544</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="18" t="s">
-        <v>534</v>
+      <c r="A39" s="16" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="18" t="s">
-        <v>535</v>
+      <c r="A40" s="16" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="16"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="16" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="16" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="16" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="16" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="16"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="16" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="16" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="16"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="16" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="16" t="s">
+        <v>554</v>
       </c>
     </row>
   </sheetData>
